--- a/test-harness/.tmp/DataElements_Export_2026-04-23.xlsx
+++ b/test-harness/.tmp/DataElements_Export_2026-04-23.xlsx
@@ -449,28 +449,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FTRrcoaog83</v>
+        <v>oIU1Fc7iLgz</v>
       </c>
       <c r="B2" t="str">
-        <v>Accute Flaccid Paralysis (Deaths &lt; 5 yrs)</v>
+        <v>1923322 Cough</v>
       </c>
       <c r="C2" t="str">
-        <v>Accute Flaccid Paral (Deaths &lt; 5 yrs)</v>
+        <v>1923322 Cough</v>
       </c>
       <c r="D2" t="str">
-        <v>DE_1148614</v>
+        <v/>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>NUMBER</v>
+        <v>BOOLEAN</v>
       </c>
       <c r="G2" t="str">
-        <v>AGGREGATE</v>
+        <v>TRACKER</v>
       </c>
       <c r="H2" t="str">
-        <v>SUM</v>
+        <v>NONE</v>
       </c>
       <c r="I2" t="str">
         <v>bjDvmb4bfuf</v>
@@ -484,34 +484,34 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>P3jJH5Tu5VC</v>
+        <v>xRydaX0ZA58</v>
       </c>
       <c r="B3" t="str">
-        <v>Acute Flaccid Paralysis (AFP) follow-up</v>
+        <v>1923322 Dose Number</v>
       </c>
       <c r="C3" t="str">
-        <v>AFP follow-up</v>
+        <v>1923322 Dose Number</v>
       </c>
       <c r="D3" t="str">
-        <v>DE_359049</v>
+        <v/>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>NUMBER</v>
+        <v>TEXT</v>
       </c>
       <c r="G3" t="str">
-        <v>AGGREGATE</v>
+        <v>TRACKER</v>
       </c>
       <c r="H3" t="str">
-        <v>SUM</v>
+        <v>NONE</v>
       </c>
       <c r="I3" t="str">
-        <v>t3aNCvHsoSn</v>
+        <v>bjDvmb4bfuf</v>
       </c>
       <c r="J3" t="str">
-        <v>Morbidity Cases</v>
+        <v>default</v>
       </c>
       <c r="K3" t="str">
         <v>false</v>
@@ -519,34 +519,34 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FQ2o8UBlcrS</v>
+        <v>JWonZPKHIba</v>
       </c>
       <c r="B4" t="str">
-        <v>Acute Flaccid Paralysis (AFP) new</v>
+        <v>1923322 Fever</v>
       </c>
       <c r="C4" t="str">
-        <v>AFP new</v>
+        <v>1923322 Fever</v>
       </c>
       <c r="D4" t="str">
-        <v>DE_388</v>
+        <v/>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>NUMBER</v>
+        <v>BOOLEAN</v>
       </c>
       <c r="G4" t="str">
-        <v>AGGREGATE</v>
+        <v>TRACKER</v>
       </c>
       <c r="H4" t="str">
-        <v>SUM</v>
+        <v>NONE</v>
       </c>
       <c r="I4" t="str">
-        <v>t3aNCvHsoSn</v>
+        <v>bjDvmb4bfuf</v>
       </c>
       <c r="J4" t="str">
-        <v>Morbidity Cases</v>
+        <v>default</v>
       </c>
       <c r="K4" t="str">
         <v>false</v>
@@ -554,34 +554,34 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>M62VHgYT2n0</v>
+        <v>UHLHF7NqOTG</v>
       </c>
       <c r="B5" t="str">
-        <v>Acute Flaccid Paralysis (AFP) referrals</v>
+        <v>1923322 Hospitalized</v>
       </c>
       <c r="C5" t="str">
-        <v>AFP referrals</v>
+        <v>1923322 Hospitalized</v>
       </c>
       <c r="D5" t="str">
-        <v>DE_358943</v>
+        <v/>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>NUMBER</v>
+        <v>BOOLEAN</v>
       </c>
       <c r="G5" t="str">
-        <v>AGGREGATE</v>
+        <v>TRACKER</v>
       </c>
       <c r="H5" t="str">
-        <v>SUM</v>
+        <v>NONE</v>
       </c>
       <c r="I5" t="str">
-        <v>ck7mRNwGDjP</v>
+        <v>bjDvmb4bfuf</v>
       </c>
       <c r="J5" t="str">
-        <v>Morbidity Referrals</v>
+        <v>default</v>
       </c>
       <c r="K5" t="str">
         <v>false</v>
@@ -589,22 +589,22 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>WO8yRIZb7nb</v>
+        <v>FrdVIoqIamG</v>
       </c>
       <c r="B6" t="str">
-        <v>Additional medication</v>
+        <v>1923322 ICU Required</v>
       </c>
       <c r="C6" t="str">
-        <v>Additional medication</v>
+        <v>1923322 ICU Required</v>
       </c>
       <c r="D6" t="str">
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Identifies any additional malaria medication provided to the case</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>TEXT</v>
+        <v>BOOLEAN</v>
       </c>
       <c r="G6" t="str">
         <v>TRACKER</v>
@@ -624,28 +624,28 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>uF1DLnZNlWe</v>
+        <v>VsDTyZG2BTe</v>
       </c>
       <c r="B7" t="str">
-        <v>Additional notes related to facility</v>
+        <v>1923322 Oxygen Level %</v>
       </c>
       <c r="C7" t="str">
-        <v>Additional notes related to facility</v>
+        <v>1923322 Oxygen Level %</v>
       </c>
       <c r="D7" t="str">
-        <v>DE_1152329</v>
+        <v/>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>LONG_TEXT</v>
+        <v>NUMBER</v>
       </c>
       <c r="G7" t="str">
-        <v>AGGREGATE</v>
+        <v>TRACKER</v>
       </c>
       <c r="H7" t="str">
-        <v>SUM</v>
+        <v>NONE</v>
       </c>
       <c r="I7" t="str">
         <v>bjDvmb4bfuf</v>
@@ -659,34 +659,34 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>eMyVanycQSC</v>
+        <v>pJu4WcEG3zY</v>
       </c>
       <c r="B8" t="str">
-        <v>Admission Date</v>
+        <v>1923322 Patient Status</v>
       </c>
       <c r="C8" t="str">
-        <v>Admission Date</v>
+        <v>1923322 Patient Status</v>
       </c>
       <c r="D8" t="str">
-        <v>DE_3000005</v>
+        <v/>
       </c>
       <c r="E8" t="str">
-        <v>Date of Admission of patient.</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>DATE</v>
+        <v>TEXT</v>
       </c>
       <c r="G8" t="str">
-        <v>TRACKER</v>
+        <v>AGGREGATE</v>
       </c>
       <c r="H8" t="str">
-        <v>AVERAGE</v>
+        <v>NONE</v>
       </c>
       <c r="I8" t="str">
-        <v>bjDvmb4bfuf</v>
+        <v>Anwp2HEiDjM</v>
       </c>
       <c r="J8" t="str">
-        <v>default</v>
+        <v>1923322 Patient Outcome Combo</v>
       </c>
       <c r="K8" t="str">
         <v>false</v>
@@ -694,28 +694,28 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>qrur9Dvnyt5</v>
+        <v>FNzKwxy99om</v>
       </c>
       <c r="B9" t="str">
-        <v>Age in years</v>
+        <v>1923322 Recovered Patients</v>
       </c>
       <c r="C9" t="str">
-        <v>Age in years</v>
+        <v>Recovered Patients</v>
       </c>
       <c r="D9" t="str">
-        <v>DE_3000003</v>
+        <v/>
       </c>
       <c r="E9" t="str">
-        <v>Age of person in years.</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>INTEGER</v>
+        <v>NUMBER</v>
       </c>
       <c r="G9" t="str">
-        <v>TRACKER</v>
+        <v>AGGREGATE</v>
       </c>
       <c r="H9" t="str">
-        <v>AVERAGE</v>
+        <v>SUM</v>
       </c>
       <c r="I9" t="str">
         <v>bjDvmb4bfuf</v>
@@ -729,28 +729,28 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>JuTpJ2Ywq5b</v>
+        <v>O50XbcOpUy4</v>
       </c>
       <c r="B10" t="str">
-        <v>Age of LLINs</v>
+        <v>1923322 Symptom Severity</v>
       </c>
       <c r="C10" t="str">
-        <v>Age of LLINs</v>
+        <v>1923322 Symptom Severity</v>
       </c>
       <c r="D10" t="str">
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>The age of the LLINs within a cases household in years</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>INTEGER_ZERO_OR_POSITIVE</v>
+        <v>TEXT</v>
       </c>
       <c r="G10" t="str">
         <v>TRACKER</v>
       </c>
       <c r="H10" t="str">
-        <v>SUM</v>
+        <v>NONE</v>
       </c>
       <c r="I10" t="str">
         <v>bjDvmb4bfuf</v>
@@ -764,16 +764,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>hCVSHjcml9g</v>
+        <v>Y3OIvJ1fg3X</v>
       </c>
       <c r="B11" t="str">
-        <v>Albendazole given at ANC (2nd trimester)</v>
+        <v>1923322 Tested Positive</v>
       </c>
       <c r="C11" t="str">
-        <v>Albendazole at ANC</v>
+        <v>Tested Postive</v>
       </c>
       <c r="D11" t="str">
-        <v>DE_359602</v>
+        <v/>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -788,10 +788,10 @@
         <v>SUM</v>
       </c>
       <c r="I11" t="str">
-        <v>KYYSTxeVw28</v>
+        <v>bjDvmb4bfuf</v>
       </c>
       <c r="J11" t="str">
-        <v>Fixed/Outreach</v>
+        <v>default</v>
       </c>
       <c r="K11" t="str">
         <v>false</v>
